--- a/server/src/templates/kp-export-template.xlsx
+++ b/server/src/templates/kp-export-template.xlsx
@@ -666,13 +666,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="13" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="13" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -986,7 +986,7 @@
     <col width="12.42578125" customWidth="1" style="95" min="1" max="1"/>
     <col width="24" customWidth="1" style="95" min="2" max="2"/>
     <col width="18" customWidth="1" style="95" min="3" max="3"/>
-    <col width="28.5703125" customWidth="1" style="95" min="4" max="4"/>
+    <col width="70" customWidth="1" style="95" min="4" max="4"/>
     <col width="16.85546875" customWidth="1" style="95" min="5" max="5"/>
     <col width="18.140625" customWidth="1" style="95" min="6" max="6"/>
     <col width="16.85546875" customWidth="1" style="95" min="7" max="7"/>
@@ -1062,7 +1062,8 @@
           <t>Предмет тендера:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="108" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="56" t="n"/>
@@ -1093,7 +1094,8 @@
           <t>Объект:</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="108" t="n"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="57" t="n"/>
@@ -1124,7 +1126,8 @@
           <t>Адрес объекта:</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="108" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="57" t="n"/>
@@ -1155,7 +1158,8 @@
           <t>Шифр рабочей документации</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="108" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="57" t="n"/>
@@ -1240,7 +1244,8 @@
           <t>Наименование контрагента</t>
         </is>
       </c>
-      <c r="D10" s="60" t="n"/>
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="108" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="57" t="n"/>
@@ -1271,7 +1276,8 @@
           <t>ИНН</t>
         </is>
       </c>
-      <c r="D11" s="60" t="n"/>
+      <c r="C11" s="60" t="n"/>
+      <c r="D11" s="108" t="n"/>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="57" t="n"/>
@@ -1302,7 +1308,8 @@
           <t>Адрес (юр., факт.)</t>
         </is>
       </c>
-      <c r="D12" s="60" t="n"/>
+      <c r="C12" s="60" t="n"/>
+      <c r="D12" s="108" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="57" t="n"/>
@@ -1381,32 +1388,32 @@
       <c r="Z14" s="6" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="95">
-      <c r="A15" s="108" t="inlineStr">
+      <c r="A15" s="109" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B15" s="109" t="inlineStr">
+      <c r="B15" s="110" t="inlineStr">
         <is>
           <t>КОД</t>
         </is>
       </c>
-      <c r="C15" s="109" t="inlineStr">
+      <c r="C15" s="110" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="D15" s="109" t="inlineStr">
+      <c r="D15" s="110" t="inlineStr">
         <is>
           <t>Наименование затрат</t>
         </is>
       </c>
-      <c r="E15" s="109" t="inlineStr">
+      <c r="E15" s="110" t="inlineStr">
         <is>
           <t>Примечание (комментарии) от контрагента</t>
         </is>
       </c>
-      <c r="F15" s="109" t="inlineStr">
+      <c r="F15" s="110" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
@@ -1426,7 +1433,7 @@
           <t>Цена за единицу, руб. с НДС 22%</t>
         </is>
       </c>
-      <c r="J15" s="110" t="n"/>
+      <c r="J15" s="108" t="n"/>
       <c r="K15" s="63" t="inlineStr">
         <is>
           <t>Цена за единицу ИТОГО, руб. с НДС 22%</t>
@@ -1437,7 +1444,7 @@
           <t>Стоимость ИТОГО, руб с НДС 22%</t>
         </is>
       </c>
-      <c r="M15" s="110" t="n"/>
+      <c r="M15" s="108" t="n"/>
       <c r="N15" s="63" t="inlineStr">
         <is>
           <t>Общая стоимость, руб. с НДС 22%</t>
@@ -1588,6 +1595,7 @@
     <row r="18" ht="15.75" customHeight="1" s="95">
       <c r="A18" s="11" t="n"/>
       <c r="B18" s="12" t="n"/>
+      <c r="C18" s="14" t="n"/>
       <c r="D18" s="14" t="n"/>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="86" t="n"/>
@@ -1615,6 +1623,7 @@
     <row r="19" ht="15.75" customHeight="1" s="95">
       <c r="A19" s="19" t="n"/>
       <c r="B19" s="85" t="n"/>
+      <c r="C19" s="22" t="n"/>
       <c r="D19" s="22" t="n"/>
       <c r="E19" s="85" t="n"/>
       <c r="F19" s="85" t="n"/>
@@ -1642,6 +1651,7 @@
     <row r="20" outlineLevel="1" s="95">
       <c r="A20" s="25" t="n"/>
       <c r="B20" s="83" t="n"/>
+      <c r="C20" s="26" t="n"/>
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="60" t="n"/>
       <c r="F20" s="83" t="n"/>
@@ -1669,6 +1679,7 @@
     <row r="21" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A21" s="32" t="n"/>
       <c r="B21" s="33" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="84" t="n"/>
@@ -1695,6 +1706,7 @@
     <row r="22" outlineLevel="1" ht="30" customHeight="1" s="95">
       <c r="A22" s="25" t="n"/>
       <c r="B22" s="83" t="n"/>
+      <c r="C22" s="26" t="n"/>
       <c r="D22" s="26" t="n"/>
       <c r="E22" s="60" t="n"/>
       <c r="F22" s="83" t="n"/>
@@ -1722,6 +1734,7 @@
     <row r="23" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A23" s="32" t="n"/>
       <c r="B23" s="33" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="84" t="n"/>
@@ -1749,6 +1762,7 @@
     <row r="24" outlineLevel="1" ht="30" customHeight="1" s="95">
       <c r="A24" s="25" t="n"/>
       <c r="B24" s="83" t="n"/>
+      <c r="C24" s="26" t="n"/>
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="60" t="n"/>
       <c r="F24" s="83" t="n"/>
@@ -1776,6 +1790,7 @@
     <row r="25" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A25" s="32" t="n"/>
       <c r="B25" s="33" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="84" t="n"/>
@@ -1803,6 +1818,7 @@
     <row r="26" ht="15.75" customHeight="1" s="95">
       <c r="A26" s="19" t="n"/>
       <c r="B26" s="21" t="n"/>
+      <c r="C26" s="22" t="n"/>
       <c r="D26" s="22" t="n"/>
       <c r="E26" s="85" t="n"/>
       <c r="F26" s="85" t="n"/>
@@ -1830,6 +1846,7 @@
     <row r="27" outlineLevel="1" ht="30" customHeight="1" s="95">
       <c r="A27" s="25" t="n"/>
       <c r="B27" s="83" t="n"/>
+      <c r="C27" s="26" t="n"/>
       <c r="D27" s="26" t="n"/>
       <c r="E27" s="60" t="n"/>
       <c r="F27" s="83" t="n"/>
@@ -1857,6 +1874,7 @@
     <row r="28" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A28" s="32" t="n"/>
       <c r="B28" s="33" t="n"/>
+      <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="84" t="n"/>
@@ -1884,6 +1902,7 @@
     <row r="29" ht="15.75" customHeight="1" s="95">
       <c r="A29" s="11" t="n"/>
       <c r="B29" s="13" t="n"/>
+      <c r="C29" s="14" t="n"/>
       <c r="D29" s="14" t="n"/>
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="86" t="n"/>
@@ -1911,6 +1930,7 @@
     <row r="30" ht="15.75" customHeight="1" s="95">
       <c r="A30" s="19" t="n"/>
       <c r="B30" s="21" t="n"/>
+      <c r="C30" s="22" t="n"/>
       <c r="D30" s="22" t="n"/>
       <c r="E30" s="85" t="n"/>
       <c r="F30" s="85" t="n"/>
@@ -1938,6 +1958,7 @@
     <row r="31" outlineLevel="1" s="95">
       <c r="A31" s="25" t="n"/>
       <c r="B31" s="83" t="n"/>
+      <c r="C31" s="26" t="n"/>
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="60" t="n"/>
       <c r="F31" s="83" t="n"/>
@@ -1965,6 +1986,7 @@
     <row r="32" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A32" s="32" t="n"/>
       <c r="B32" s="33" t="n"/>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="84" t="n"/>
@@ -1992,6 +2014,7 @@
     <row r="33" outlineLevel="1" s="95">
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="83" t="n"/>
+      <c r="C33" s="26" t="n"/>
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="60" t="n"/>
       <c r="F33" s="83" t="n"/>
@@ -2019,6 +2042,7 @@
     <row r="34" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A34" s="32" t="n"/>
       <c r="B34" s="33" t="n"/>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="84" t="n"/>
@@ -2046,6 +2070,7 @@
     <row r="35" outlineLevel="1" ht="30" customHeight="1" s="95">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="83" t="n"/>
+      <c r="C35" s="26" t="n"/>
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="60" t="n"/>
       <c r="F35" s="83" t="n"/>
@@ -2073,6 +2098,7 @@
     <row r="36" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A36" s="32" t="n"/>
       <c r="B36" s="33" t="n"/>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="84" t="n"/>
@@ -2100,6 +2126,7 @@
     <row r="37" ht="15.75" customHeight="1" s="95">
       <c r="A37" s="19" t="n"/>
       <c r="B37" s="21" t="n"/>
+      <c r="C37" s="22" t="n"/>
       <c r="D37" s="22" t="n"/>
       <c r="E37" s="85" t="n"/>
       <c r="F37" s="85" t="n"/>
@@ -2127,6 +2154,7 @@
     <row r="38" outlineLevel="1" ht="30" customHeight="1" s="95">
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="83" t="n"/>
+      <c r="C38" s="26" t="n"/>
       <c r="D38" s="26" t="n"/>
       <c r="E38" s="60" t="n"/>
       <c r="F38" s="83" t="n"/>
@@ -2154,6 +2182,7 @@
     <row r="39" outlineLevel="3" ht="15.75" customHeight="1" s="95">
       <c r="A39" s="32" t="n"/>
       <c r="B39" s="33" t="n"/>
+      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="84" t="n"/>
@@ -2181,6 +2210,7 @@
     <row r="40" ht="15.75" customHeight="1" s="95">
       <c r="A40" s="39" t="n"/>
       <c r="B40" s="40" t="n"/>
+      <c r="C40" s="41" t="n"/>
       <c r="D40" s="41" t="n"/>
       <c r="E40" s="42" t="n"/>
       <c r="F40" s="42" t="n"/>
@@ -2208,6 +2238,7 @@
     <row r="41" ht="15.75" customHeight="1" s="95">
       <c r="A41" s="39" t="n"/>
       <c r="B41" s="40" t="n"/>
+      <c r="C41" s="41" t="n"/>
       <c r="D41" s="41" t="n"/>
       <c r="E41" s="42" t="n"/>
       <c r="F41" s="42" t="n"/>
@@ -3186,12 +3217,12 @@
       <c r="B74" s="115" t="n"/>
       <c r="C74" s="115" t="n"/>
       <c r="D74" s="115" t="n"/>
-      <c r="E74" s="110" t="n"/>
+      <c r="E74" s="108" t="n"/>
       <c r="F74" s="53" t="n"/>
       <c r="G74" s="116" t="n"/>
       <c r="H74" s="115" t="n"/>
       <c r="I74" s="115" t="n"/>
-      <c r="J74" s="110" t="n"/>
+      <c r="J74" s="108" t="n"/>
       <c r="K74" s="57" t="n"/>
       <c r="L74" s="57" t="n"/>
       <c r="M74" s="57" t="n"/>
@@ -3220,7 +3251,7 @@
       </c>
       <c r="C75" s="115" t="n"/>
       <c r="D75" s="115" t="n"/>
-      <c r="E75" s="110" t="n"/>
+      <c r="E75" s="108" t="n"/>
       <c r="F75" s="55" t="inlineStr">
         <is>
           <t>да (%) /нет</t>
@@ -3229,7 +3260,7 @@
       <c r="G75" s="60" t="n"/>
       <c r="H75" s="115" t="n"/>
       <c r="I75" s="115" t="n"/>
-      <c r="J75" s="110" t="n"/>
+      <c r="J75" s="108" t="n"/>
       <c r="K75" s="57" t="n"/>
       <c r="L75" s="57" t="n"/>
       <c r="M75" s="57" t="n"/>
@@ -3258,7 +3289,7 @@
       </c>
       <c r="C76" s="115" t="n"/>
       <c r="D76" s="115" t="n"/>
-      <c r="E76" s="110" t="n"/>
+      <c r="E76" s="108" t="n"/>
       <c r="F76" s="55" t="inlineStr">
         <is>
           <t>да /нет</t>
@@ -3267,7 +3298,7 @@
       <c r="G76" s="60" t="n"/>
       <c r="H76" s="115" t="n"/>
       <c r="I76" s="115" t="n"/>
-      <c r="J76" s="110" t="n"/>
+      <c r="J76" s="108" t="n"/>
       <c r="K76" s="57" t="n"/>
       <c r="L76" s="57" t="n"/>
       <c r="M76" s="57" t="n"/>
@@ -3296,7 +3327,7 @@
       </c>
       <c r="C77" s="115" t="n"/>
       <c r="D77" s="115" t="n"/>
-      <c r="E77" s="110" t="n"/>
+      <c r="E77" s="108" t="n"/>
       <c r="F77" s="55" t="inlineStr">
         <is>
           <t>да(банк) /нет</t>
@@ -3305,7 +3336,7 @@
       <c r="G77" s="60" t="n"/>
       <c r="H77" s="115" t="n"/>
       <c r="I77" s="115" t="n"/>
-      <c r="J77" s="110" t="n"/>
+      <c r="J77" s="108" t="n"/>
       <c r="K77" s="57" t="n"/>
       <c r="L77" s="57" t="n"/>
       <c r="M77" s="57" t="n"/>
@@ -3334,7 +3365,7 @@
       </c>
       <c r="C78" s="115" t="n"/>
       <c r="D78" s="115" t="n"/>
-      <c r="E78" s="110" t="n"/>
+      <c r="E78" s="108" t="n"/>
       <c r="F78" s="55" t="inlineStr">
         <is>
           <t>мес.</t>
@@ -3343,7 +3374,7 @@
       <c r="G78" s="60" t="n"/>
       <c r="H78" s="115" t="n"/>
       <c r="I78" s="115" t="n"/>
-      <c r="J78" s="110" t="n"/>
+      <c r="J78" s="108" t="n"/>
       <c r="K78" s="57" t="n"/>
       <c r="L78" s="57" t="n"/>
       <c r="M78" s="57" t="n"/>
@@ -3372,7 +3403,7 @@
       </c>
       <c r="C79" s="115" t="n"/>
       <c r="D79" s="115" t="n"/>
-      <c r="E79" s="110" t="n"/>
+      <c r="E79" s="108" t="n"/>
       <c r="F79" s="55" t="inlineStr">
         <is>
           <t>да /нет</t>
@@ -3381,7 +3412,7 @@
       <c r="G79" s="60" t="n"/>
       <c r="H79" s="115" t="n"/>
       <c r="I79" s="115" t="n"/>
-      <c r="J79" s="110" t="n"/>
+      <c r="J79" s="108" t="n"/>
       <c r="K79" s="57" t="n"/>
       <c r="L79" s="57" t="n"/>
       <c r="M79" s="57" t="n"/>
@@ -3410,7 +3441,7 @@
       </c>
       <c r="C80" s="115" t="n"/>
       <c r="D80" s="115" t="n"/>
-      <c r="E80" s="110" t="n"/>
+      <c r="E80" s="108" t="n"/>
       <c r="F80" s="55" t="inlineStr">
         <is>
           <t>были/не были
@@ -3420,7 +3451,7 @@
       <c r="G80" s="60" t="n"/>
       <c r="H80" s="115" t="n"/>
       <c r="I80" s="115" t="n"/>
-      <c r="J80" s="110" t="n"/>
+      <c r="J80" s="108" t="n"/>
       <c r="K80" s="57" t="n"/>
       <c r="L80" s="57" t="n"/>
       <c r="M80" s="57" t="n"/>
@@ -3449,7 +3480,7 @@
       </c>
       <c r="C81" s="115" t="n"/>
       <c r="D81" s="115" t="n"/>
-      <c r="E81" s="110" t="n"/>
+      <c r="E81" s="108" t="n"/>
       <c r="F81" s="55" t="inlineStr">
         <is>
           <t>да/нет</t>
@@ -3458,7 +3489,7 @@
       <c r="G81" s="60" t="n"/>
       <c r="H81" s="115" t="n"/>
       <c r="I81" s="115" t="n"/>
-      <c r="J81" s="110" t="n"/>
+      <c r="J81" s="108" t="n"/>
       <c r="K81" s="57" t="n"/>
       <c r="L81" s="57" t="n"/>
       <c r="M81" s="57" t="n"/>
@@ -3487,7 +3518,7 @@
       </c>
       <c r="C82" s="115" t="n"/>
       <c r="D82" s="115" t="n"/>
-      <c r="E82" s="110" t="n"/>
+      <c r="E82" s="108" t="n"/>
       <c r="F82" s="55" t="inlineStr">
         <is>
           <t>да (сумма) /нет</t>
@@ -3496,7 +3527,7 @@
       <c r="G82" s="60" t="n"/>
       <c r="H82" s="115" t="n"/>
       <c r="I82" s="115" t="n"/>
-      <c r="J82" s="110" t="n"/>
+      <c r="J82" s="108" t="n"/>
       <c r="K82" s="57" t="n"/>
       <c r="L82" s="57" t="n"/>
       <c r="M82" s="57" t="n"/>
@@ -3525,7 +3556,7 @@
       </c>
       <c r="C83" s="115" t="n"/>
       <c r="D83" s="115" t="n"/>
-      <c r="E83" s="110" t="n"/>
+      <c r="E83" s="108" t="n"/>
       <c r="F83" s="55" t="inlineStr">
         <is>
           <t>кол-во/кол-во</t>
@@ -3534,7 +3565,7 @@
       <c r="G83" s="60" t="n"/>
       <c r="H83" s="115" t="n"/>
       <c r="I83" s="115" t="n"/>
-      <c r="J83" s="110" t="n"/>
+      <c r="J83" s="108" t="n"/>
       <c r="K83" s="57" t="n"/>
       <c r="L83" s="57" t="n"/>
       <c r="M83" s="57" t="n"/>
@@ -3563,7 +3594,7 @@
       </c>
       <c r="C84" s="115" t="n"/>
       <c r="D84" s="115" t="n"/>
-      <c r="E84" s="110" t="n"/>
+      <c r="E84" s="108" t="n"/>
       <c r="F84" s="55" t="inlineStr">
         <is>
           <t>дд/мм/гг</t>
@@ -3572,7 +3603,7 @@
       <c r="G84" s="60" t="n"/>
       <c r="H84" s="115" t="n"/>
       <c r="I84" s="115" t="n"/>
-      <c r="J84" s="110" t="n"/>
+      <c r="J84" s="108" t="n"/>
       <c r="K84" s="57" t="n"/>
       <c r="L84" s="57" t="n"/>
       <c r="M84" s="57" t="n"/>
@@ -3601,7 +3632,7 @@
       </c>
       <c r="C85" s="115" t="n"/>
       <c r="D85" s="115" t="n"/>
-      <c r="E85" s="110" t="n"/>
+      <c r="E85" s="108" t="n"/>
       <c r="F85" s="55" t="inlineStr">
         <is>
           <t>год-сумма/год-сумма/год-сумма (руб.без НДС)</t>
@@ -3616,7 +3647,7 @@
       </c>
       <c r="H85" s="115" t="n"/>
       <c r="I85" s="115" t="n"/>
-      <c r="J85" s="110" t="n"/>
+      <c r="J85" s="108" t="n"/>
       <c r="K85" s="57" t="n"/>
       <c r="L85" s="57" t="n"/>
       <c r="M85" s="57" t="n"/>
@@ -3645,7 +3676,7 @@
       </c>
       <c r="C86" s="115" t="n"/>
       <c r="D86" s="115" t="n"/>
-      <c r="E86" s="110" t="n"/>
+      <c r="E86" s="108" t="n"/>
       <c r="F86" s="55" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3654,7 +3685,7 @@
       <c r="G86" s="60" t="n"/>
       <c r="H86" s="115" t="n"/>
       <c r="I86" s="115" t="n"/>
-      <c r="J86" s="110" t="n"/>
+      <c r="J86" s="108" t="n"/>
       <c r="K86" s="57" t="n"/>
       <c r="L86" s="57" t="n"/>
       <c r="M86" s="57" t="n"/>
@@ -3683,12 +3714,12 @@
       </c>
       <c r="C87" s="115" t="n"/>
       <c r="D87" s="115" t="n"/>
-      <c r="E87" s="110" t="n"/>
+      <c r="E87" s="108" t="n"/>
       <c r="F87" s="55" t="n"/>
       <c r="G87" s="60" t="n"/>
       <c r="H87" s="115" t="n"/>
       <c r="I87" s="115" t="n"/>
-      <c r="J87" s="110" t="n"/>
+      <c r="J87" s="108" t="n"/>
       <c r="K87" s="57" t="n"/>
       <c r="L87" s="57" t="n"/>
       <c r="M87" s="57" t="n"/>
@@ -3717,12 +3748,12 @@
       </c>
       <c r="C88" s="115" t="n"/>
       <c r="D88" s="115" t="n"/>
-      <c r="E88" s="110" t="n"/>
+      <c r="E88" s="108" t="n"/>
       <c r="F88" s="55" t="n"/>
       <c r="G88" s="60" t="n"/>
       <c r="H88" s="115" t="n"/>
       <c r="I88" s="115" t="n"/>
-      <c r="J88" s="110" t="n"/>
+      <c r="J88" s="108" t="n"/>
       <c r="K88" s="57" t="n"/>
       <c r="L88" s="57" t="n"/>
       <c r="M88" s="57" t="n"/>
@@ -3751,12 +3782,12 @@
       </c>
       <c r="C89" s="115" t="n"/>
       <c r="D89" s="115" t="n"/>
-      <c r="E89" s="110" t="n"/>
+      <c r="E89" s="108" t="n"/>
       <c r="F89" s="55" t="n"/>
       <c r="G89" s="60" t="n"/>
       <c r="H89" s="115" t="n"/>
       <c r="I89" s="115" t="n"/>
-      <c r="J89" s="110" t="n"/>
+      <c r="J89" s="108" t="n"/>
       <c r="K89" s="57" t="n"/>
       <c r="L89" s="57" t="n"/>
       <c r="M89" s="57" t="n"/>
@@ -28697,8 +28728,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A17:N41"/>
-  <mergeCells count="49">
+  <mergeCells count="56">
     <mergeCell ref="G88:J88"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="B80:E80"/>
     <mergeCell ref="B89:E89"/>
@@ -28710,11 +28742,13 @@
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="A63:O63"/>
     <mergeCell ref="A68:O68"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="H15:H16"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G87:J87"/>
     <mergeCell ref="B78:E78"/>
@@ -28727,17 +28761,21 @@
     <mergeCell ref="B83:E83"/>
     <mergeCell ref="G79:J79"/>
     <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="G85:J85"/>
     <mergeCell ref="B1:O2"/>
     <mergeCell ref="B85:E85"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="G84:J84"/>
     <mergeCell ref="G75:J75"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="L15:M15"/>
     <mergeCell ref="G77:J77"/>
     <mergeCell ref="G86:J86"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A62:O62"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="N15:N16"/>
     <mergeCell ref="B88:E88"/>
